--- a/AAII_Financials/Quarterly/VIVC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VIVC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>VIVC</t>
   </si>
@@ -656,144 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42947</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
+      <c r="D8" s="3">
+        <v>800</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
@@ -801,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>200</v>
-      </c>
-      <c r="K8" s="3">
-        <v>100</v>
       </c>
       <c r="L8" s="3">
         <v>100</v>
       </c>
       <c r="M8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -819,26 +823,26 @@
         <v>0</v>
       </c>
       <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>100</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
@@ -860,20 +864,23 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="3">
+        <v>700</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
@@ -884,34 +891,34 @@
         <v>0</v>
       </c>
       <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
       <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
         <v>200</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3">
-        <v>0</v>
+      <c r="N9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>0</v>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R9" s="3">
         <v>0</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
+      <c r="S9" s="3">
+        <v>0</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
@@ -931,8 +938,8 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z9" s="3">
-        <v>0</v>
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA9" s="3">
         <v>0</v>
@@ -940,26 +947,29 @@
       <c r="AB9" s="3">
         <v>0</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
         <v>-100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
       <c r="H10" s="3">
         <v>0</v>
       </c>
@@ -967,35 +977,35 @@
         <v>0</v>
       </c>
       <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
         <v>-200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3">
-        <v>0</v>
+      <c r="N10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3">
         <v>100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>400</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1014,8 +1024,8 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z10" s="3">
-        <v>0</v>
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA10" s="3">
         <v>0</v>
@@ -1023,11 +1033,14 @@
       <c r="AB10" s="3">
         <v>0</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1247,22 +1267,22 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>1400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1800</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
@@ -1270,12 +1290,12 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1291,8 +1311,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1306,8 +1326,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,59 +1443,60 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>800</v>
+      </c>
+      <c r="E17" s="3">
         <v>100</v>
       </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
       <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L17" s="3">
+        <v>600</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N17" s="3">
+        <v>900</v>
+      </c>
+      <c r="O17" s="3">
+        <v>400</v>
+      </c>
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3">
-        <v>3000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>600</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M17" s="3">
-        <v>900</v>
-      </c>
-      <c r="N17" s="3">
-        <v>400</v>
-      </c>
-      <c r="O17" s="3">
-        <v>300</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>800</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
       <c r="T17" s="3">
         <v>0</v>
       </c>
@@ -1497,71 +1524,74 @@
       <c r="AB17" s="3">
         <v>0</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0</v>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F18" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3">
         <v>-300</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-500</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-900</v>
       </c>
       <c r="M18" s="3">
         <v>-900</v>
       </c>
       <c r="N18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O18" s="3">
         <v>-400</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-300</v>
       </c>
       <c r="P18" s="3">
         <v>-300</v>
       </c>
       <c r="Q18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>100</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
         <v>0</v>
       </c>
@@ -1580,11 +1610,14 @@
       <c r="AB18" s="3">
         <v>0</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,23 +1647,24 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1638,23 +1672,23 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
       </c>
       <c r="L20" s="3">
+        <v>200</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1694,46 +1728,49 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-100</v>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F21" s="3">
         <v>-100</v>
       </c>
       <c r="G21" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="H21" s="3">
         <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-2500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-400</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-900</v>
       </c>
       <c r="M21" s="3">
         <v>-900</v>
       </c>
       <c r="N21" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="O21" s="3">
         <v>-300</v>
@@ -1742,23 +1779,23 @@
         <v>-300</v>
       </c>
       <c r="Q21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-300</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>100</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
       <c r="W21" s="3">
         <v>0</v>
       </c>
@@ -1771,8 +1808,8 @@
       <c r="Z21" s="3">
         <v>0</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
+      <c r="AA21" s="3">
+        <v>0</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
@@ -1780,8 +1817,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1830,8 +1870,8 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1848,8 +1888,8 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -1863,68 +1903,71 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3">
         <v>-100</v>
       </c>
       <c r="F23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G23" s="3">
         <v>-200</v>
       </c>
-      <c r="G23" s="3">
-        <v>-300</v>
-      </c>
       <c r="H23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-400</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-900</v>
       </c>
       <c r="M23" s="3">
         <v>-900</v>
       </c>
       <c r="N23" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="O23" s="3">
         <v>-300</v>
       </c>
       <c r="P23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>100</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
         <v>0</v>
       </c>
@@ -1943,11 +1986,14 @@
       <c r="AB23" s="3">
         <v>0</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1981,14 +2027,14 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1997,13 +2043,13 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T24" s="3">
         <v>100</v>
       </c>
       <c r="U24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -2029,8 +2075,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,68 +2161,71 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
         <v>-100</v>
       </c>
       <c r="F26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
-        <v>-300</v>
-      </c>
       <c r="H26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-400</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-900</v>
       </c>
       <c r="M26" s="3">
         <v>-900</v>
       </c>
       <c r="N26" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="O26" s="3">
         <v>-300</v>
       </c>
       <c r="P26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>100</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
         <v>0</v>
       </c>
@@ -2192,71 +2244,74 @@
       <c r="AB26" s="3">
         <v>0</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
         <v>-100</v>
       </c>
       <c r="F27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G27" s="3">
         <v>-200</v>
       </c>
-      <c r="G27" s="3">
-        <v>-300</v>
-      </c>
       <c r="H27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-900</v>
       </c>
       <c r="M27" s="3">
         <v>-900</v>
       </c>
       <c r="N27" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="O27" s="3">
         <v>-300</v>
       </c>
       <c r="P27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-400</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>100</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
         <v>0</v>
       </c>
@@ -2275,11 +2330,14 @@
       <c r="AB27" s="3">
         <v>0</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,37 +2419,40 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E29" s="3">
         <v>100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-200</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="I29" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="J29" s="3">
         <v>-100</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="K29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,23 +2677,26 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -2634,23 +2704,23 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
       </c>
       <c r="L32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2690,71 +2760,74 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-300</v>
       </c>
       <c r="H33" s="3">
         <v>-300</v>
       </c>
       <c r="I33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J33" s="3">
         <v>-200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-900</v>
       </c>
       <c r="M33" s="3">
         <v>-900</v>
       </c>
       <c r="N33" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="O33" s="3">
         <v>-300</v>
       </c>
       <c r="P33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-400</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>100</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
         <v>0</v>
       </c>
@@ -2773,11 +2846,14 @@
       <c r="AB33" s="3">
         <v>0</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,68 +2935,71 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-300</v>
       </c>
       <c r="H35" s="3">
         <v>-300</v>
       </c>
       <c r="I35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J35" s="3">
         <v>-200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-900</v>
       </c>
       <c r="M35" s="3">
         <v>-900</v>
       </c>
       <c r="N35" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="O35" s="3">
         <v>-300</v>
       </c>
       <c r="P35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-400</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>100</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
         <v>0</v>
       </c>
@@ -2939,99 +3018,105 @@
       <c r="AB35" s="3">
         <v>0</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42947</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,19 +3178,20 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
         <v>900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>300</v>
-      </c>
-      <c r="F41" s="3">
-        <v>100</v>
       </c>
       <c r="G41" s="3">
         <v>100</v>
@@ -3113,47 +3200,47 @@
         <v>100</v>
       </c>
       <c r="I41" s="3">
+        <v>100</v>
+      </c>
+      <c r="J41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>100</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
       <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>200</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
       <c r="W41" s="3">
         <v>0</v>
       </c>
@@ -3172,11 +3259,14 @@
       <c r="AB41" s="3">
         <v>0</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,16 +3348,19 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="D43" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
@@ -3290,33 +3383,33 @@
       <c r="L43" s="3">
         <v>0</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
+      <c r="M43" s="3">
+        <v>0</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
       <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3329,8 +3422,8 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -3341,28 +3434,31 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>100</v>
+      </c>
+      <c r="E44" s="3">
         <v>800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>900</v>
-      </c>
-      <c r="F44" s="3">
-        <v>1500</v>
       </c>
       <c r="G44" s="3">
         <v>1500</v>
       </c>
       <c r="H44" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I44" s="3">
         <v>1300</v>
-      </c>
-      <c r="I44" s="3">
-        <v>200</v>
       </c>
       <c r="J44" s="3">
         <v>200</v>
@@ -3371,16 +3467,16 @@
         <v>200</v>
       </c>
       <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3424,25 +3520,28 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>300</v>
       </c>
       <c r="I45" s="3">
         <v>300</v>
@@ -3451,28 +3550,28 @@
         <v>300</v>
       </c>
       <c r="K45" s="3">
+        <v>300</v>
+      </c>
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
-      </c>
-      <c r="P45" s="3">
-        <v>100</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
       </c>
       <c r="R45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S45" s="3">
         <v>0</v>
@@ -3504,71 +3603,74 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1000</v>
-      </c>
-      <c r="N46" s="3">
-        <v>600</v>
       </c>
       <c r="O46" s="3">
         <v>600</v>
       </c>
       <c r="P46" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q46" s="3">
         <v>300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>500</v>
-      </c>
-      <c r="R46" s="3">
-        <v>600</v>
       </c>
       <c r="S46" s="3">
         <v>600</v>
       </c>
       <c r="T46" s="3">
+        <v>600</v>
+      </c>
+      <c r="U46" s="3">
         <v>500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>200</v>
       </c>
-      <c r="V46" s="3">
-        <v>0</v>
-      </c>
       <c r="W46" s="3">
         <v>0</v>
       </c>
@@ -3587,11 +3689,14 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3601,8 +3706,8 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3">
         <v>0</v>
@@ -3614,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K47" s="3">
         <v>100</v>
@@ -3623,13 +3728,13 @@
         <v>100</v>
       </c>
       <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3673,8 +3778,11 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3682,31 +3790,31 @@
         <v>0</v>
       </c>
       <c r="E48" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3">
         <v>800</v>
       </c>
       <c r="G48" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H48" s="3">
         <v>700</v>
       </c>
       <c r="I48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="J48" s="3">
         <v>800</v>
       </c>
       <c r="K48" s="3">
+        <v>800</v>
+      </c>
+      <c r="L48" s="3">
         <v>1000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>900</v>
-      </c>
-      <c r="M48" s="3">
-        <v>200</v>
       </c>
       <c r="N48" s="3">
         <v>200</v>
@@ -3718,19 +3826,19 @@
         <v>200</v>
       </c>
       <c r="Q48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R48" s="3">
         <v>300</v>
       </c>
       <c r="S48" s="3">
-        <v>0</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U48" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3750,14 +3858,17 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
+      <c r="AB48" s="3">
+        <v>0</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3776,8 +3887,8 @@
       <c r="H49" s="3">
         <v>0</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+      <c r="I49" s="3">
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -3794,8 +3905,8 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,23 +4122,26 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>2700</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
       <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
         <v>2700</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
@@ -4037,14 +4157,14 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -4067,14 +4187,14 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
+      <c r="W52" s="3">
+        <v>0</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,68 +4294,71 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E54" s="3">
         <v>5500</v>
-      </c>
-      <c r="E54" s="3">
-        <v>3200</v>
       </c>
       <c r="F54" s="3">
         <v>3200</v>
       </c>
       <c r="G54" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H54" s="3">
         <v>2600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1300</v>
-      </c>
-      <c r="N54" s="3">
-        <v>900</v>
       </c>
       <c r="O54" s="3">
         <v>900</v>
       </c>
       <c r="P54" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q54" s="3">
         <v>600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>200</v>
       </c>
-      <c r="V54" s="3">
-        <v>0</v>
-      </c>
       <c r="W54" s="3">
         <v>0</v>
       </c>
@@ -4251,11 +4377,14 @@
       <c r="AB54" s="3">
         <v>0</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,8 +4446,9 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4325,29 +4456,29 @@
         <v>0</v>
       </c>
       <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
       <c r="G57" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H57" s="3">
         <v>600</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
       </c>
       <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -4366,8 +4497,8 @@
       <c r="R57" s="3">
         <v>0</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="S57" s="3">
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -4375,11 +4506,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
@@ -4387,8 +4518,8 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA57" s="3">
         <v>0</v>
@@ -4399,8 +4530,11 @@
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4428,15 +4562,15 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
         <v>200</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -4449,8 +4583,8 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -4461,8 +4595,8 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4479,73 +4613,76 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>500</v>
-      </c>
-      <c r="M59" s="3">
-        <v>600</v>
       </c>
       <c r="N59" s="3">
         <v>600</v>
       </c>
       <c r="O59" s="3">
+        <v>600</v>
+      </c>
+      <c r="P59" s="3">
         <v>300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1000</v>
       </c>
       <c r="R59" s="3">
         <v>1000</v>
       </c>
       <c r="S59" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="T59" s="3">
         <v>300</v>
       </c>
       <c r="U59" s="3">
+        <v>300</v>
+      </c>
+      <c r="V59" s="3">
         <v>100</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
+      <c r="W59" s="3">
+        <v>0</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
@@ -4556,77 +4693,80 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB59" s="3">
+        <v>0</v>
       </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>1000</v>
       </c>
       <c r="R60" s="3">
         <v>1000</v>
       </c>
       <c r="S60" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="T60" s="3">
         <v>300</v>
       </c>
       <c r="U60" s="3">
+        <v>300</v>
+      </c>
+      <c r="V60" s="3">
         <v>100</v>
       </c>
-      <c r="V60" s="3">
-        <v>0</v>
-      </c>
       <c r="W60" s="3">
         <v>0</v>
       </c>
@@ -4645,11 +4785,14 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4657,7 +4800,7 @@
         <v>600</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
@@ -4690,7 +4833,7 @@
         <v>100</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -4731,28 +4874,31 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>2300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>300</v>
       </c>
       <c r="H62" s="3">
         <v>300</v>
       </c>
       <c r="I62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J62" s="3">
         <v>400</v>
@@ -4761,16 +4907,16 @@
         <v>400</v>
       </c>
       <c r="L62" s="3">
+        <v>400</v>
+      </c>
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,68 +5218,71 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E66" s="3">
         <v>5700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1500</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1100</v>
       </c>
       <c r="L66" s="3">
         <v>1100</v>
       </c>
       <c r="M66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N66" s="3">
         <v>1000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>1100</v>
       </c>
       <c r="R66" s="3">
         <v>1100</v>
       </c>
       <c r="S66" s="3">
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="T66" s="3">
         <v>300</v>
       </c>
       <c r="U66" s="3">
+        <v>300</v>
+      </c>
+      <c r="V66" s="3">
         <v>100</v>
       </c>
-      <c r="V66" s="3">
-        <v>0</v>
-      </c>
       <c r="W66" s="3">
         <v>0</v>
       </c>
@@ -5143,11 +5301,14 @@
       <c r="AB66" s="3">
         <v>0</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,64 +5680,67 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-5100</v>
+        <v>-3300</v>
       </c>
       <c r="E72" s="3">
         <v>-5100</v>
       </c>
       <c r="F72" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="G72" s="3">
         <v>-4800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-4300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-4000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-300</v>
-      </c>
-      <c r="S72" s="3">
-        <v>200</v>
       </c>
       <c r="T72" s="3">
         <v>200</v>
       </c>
       <c r="U72" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V72" s="3">
         <v>0</v>
@@ -5589,11 +5763,14 @@
       <c r="AB72" s="3">
         <v>0</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,68 +6024,71 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-100</v>
       </c>
-      <c r="J76" s="3">
-        <v>0</v>
-      </c>
       <c r="K76" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="L76" s="3">
         <v>400</v>
       </c>
       <c r="M76" s="3">
+        <v>400</v>
+      </c>
+      <c r="N76" s="3">
         <v>300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>100</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
       <c r="W76" s="3">
         <v>0</v>
       </c>
@@ -5921,11 +6107,14 @@
       <c r="AB76" s="3">
         <v>0</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,156 +6196,162 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42947</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-300</v>
       </c>
       <c r="H81" s="3">
         <v>-300</v>
       </c>
       <c r="I81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J81" s="3">
         <v>-200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-900</v>
       </c>
       <c r="M81" s="3">
         <v>-900</v>
       </c>
       <c r="N81" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="O81" s="3">
         <v>-300</v>
       </c>
       <c r="P81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-400</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>100</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
         <v>0</v>
       </c>
@@ -6175,11 +6370,14 @@
       <c r="AB81" s="3">
         <v>0</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6259,11 +6458,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -6283,8 +6482,8 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
+      <c r="AA83" s="3">
+        <v>0</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,65 +6921,68 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>700</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="L89" s="3">
+        <v>100</v>
+      </c>
+      <c r="M89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
-        <v>700</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S89" s="3">
+        <v>300</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3">
         <v>100</v>
       </c>
-      <c r="L89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-700</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R89" s="3">
-        <v>300</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3">
-        <v>100</v>
-      </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
         <v>0</v>
       </c>
@@ -6787,11 +7004,14 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6848,11 +7069,11 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6868,11 +7089,11 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -6889,8 +7110,8 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -6901,11 +7122,14 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,8 +7297,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7079,34 +7309,34 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F94" s="3">
         <v>-100</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3">
         <v>100</v>
       </c>
       <c r="J94" s="3">
+        <v>100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-400</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-200</v>
       </c>
       <c r="L94" s="3">
         <v>-200</v>
       </c>
       <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -7117,17 +7347,17 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -7150,11 +7380,14 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,67 +7759,70 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
-      </c>
-      <c r="F100" s="3">
-        <v>200</v>
       </c>
       <c r="G100" s="3">
         <v>200</v>
       </c>
       <c r="H100" s="3">
+        <v>200</v>
+      </c>
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>900</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3">
-        <v>100</v>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U100" s="3">
         <v>100</v>
       </c>
       <c r="V100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -7596,11 +7842,14 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7649,8 +7898,8 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
@@ -7667,8 +7916,8 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -7682,67 +7931,70 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>400</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3">
-        <v>200</v>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U102" s="3">
         <v>200</v>
       </c>
       <c r="V102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
@@ -7762,7 +8014,10 @@
       <c r="AB102" s="3">
         <v>0</v>
       </c>
-      <c r="AC102" s="3" t="s">
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VIVC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VIVC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>VIVC</t>
   </si>
@@ -656,198 +656,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43312</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43220</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43131</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42947</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E8" s="3">
         <v>800</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
+        <v>800</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>200</v>
+      </c>
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="O8" s="3">
+        <v>100</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
         <v>200</v>
-      </c>
-      <c r="L8" s="3">
-        <v>100</v>
-      </c>
-      <c r="M8" s="3">
-        <v>100</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>200</v>
-      </c>
-      <c r="R8" s="3">
-        <v>100</v>
-      </c>
-      <c r="S8" s="3">
-        <v>400</v>
       </c>
       <c r="T8" s="3">
         <v>100</v>
       </c>
       <c r="U8" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="V8" s="3">
         <v>100</v>
       </c>
       <c r="W8" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="X8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
@@ -867,64 +874,70 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>600</v>
+      </c>
+      <c r="E9" s="3">
         <v>700</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F9" s="3">
-        <v>100</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
       </c>
       <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
       </c>
       <c r="R9" s="3">
         <v>0</v>
       </c>
-      <c r="S9" s="3">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3">
+        <v>0</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
@@ -941,77 +954,83 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>0</v>
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC9" s="3">
         <v>0</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N10" s="3">
+        <v>100</v>
+      </c>
+      <c r="O10" s="3">
         <v>-100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>100</v>
-      </c>
-      <c r="M10" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3">
-        <v>100</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>400</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1027,20 +1046,26 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>0</v>
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC10" s="3">
         <v>0</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,8 +1096,10 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1157,8 +1184,14 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,16 +1276,22 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1270,38 +1309,38 @@
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>1800</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,11 +1353,11 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1329,8 +1368,14 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1415,8 +1460,14 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,65 +1495,67 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E17" s="3">
         <v>800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>800</v>
+      </c>
+      <c r="G17" s="3">
         <v>100</v>
       </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>400</v>
-      </c>
       <c r="H17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="3">
         <v>100</v>
       </c>
       <c r="J17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17" s="3">
+        <v>100</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
         <v>3000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>800</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
       <c r="V17" s="3">
         <v>0</v>
       </c>
@@ -1527,76 +1580,82 @@
       <c r="AC17" s="3">
         <v>0</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
+        <v>700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
       </c>
-      <c r="G18" s="3">
-        <v>-300</v>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
         <v>-100</v>
       </c>
       <c r="J18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
         <v>-2800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-400</v>
-      </c>
-      <c r="T18" s="3">
-        <v>100</v>
-      </c>
-      <c r="U18" s="3">
-        <v>300</v>
       </c>
       <c r="V18" s="3">
         <v>100</v>
       </c>
       <c r="W18" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="X18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y18" s="3">
         <v>0</v>
@@ -1613,11 +1672,17 @@
       <c r="AC18" s="3">
         <v>0</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,53 +1713,55 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
+      <c r="E20" s="3">
+        <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>200</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1731,28 +1798,34 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
+        <v>800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
       </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3">
         <v>-100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
       </c>
       <c r="I21" s="3">
         <v>-100</v>
@@ -1761,47 +1834,47 @@
         <v>0</v>
       </c>
       <c r="K21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
         <v>-2500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-900</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-300</v>
       </c>
       <c r="Q21" s="3">
         <v>-300</v>
       </c>
       <c r="R21" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="S21" s="3">
         <v>-300</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
+      <c r="T21" s="3">
+        <v>-100</v>
       </c>
       <c r="U21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>100</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
-      <c r="X21" s="3">
-        <v>0</v>
-      </c>
       <c r="Y21" s="3">
         <v>0</v>
       </c>
@@ -1811,17 +1884,23 @@
       <c r="AA21" s="3">
         <v>0</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
+      <c r="AB21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>0</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1873,11 +1952,11 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1891,11 +1970,11 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1906,22 +1985,28 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
         <v>-100</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-200</v>
       </c>
       <c r="H23" s="3">
         <v>-100</v>
@@ -1930,49 +2015,49 @@
         <v>-100</v>
       </c>
       <c r="J23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>-2600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-300</v>
-      </c>
-      <c r="T23" s="3">
-        <v>100</v>
-      </c>
-      <c r="U23" s="3">
-        <v>200</v>
       </c>
       <c r="V23" s="3">
         <v>100</v>
       </c>
       <c r="W23" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y23" s="3">
         <v>0</v>
@@ -1989,16 +2074,22 @@
       <c r="AC23" s="3">
         <v>0</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -2030,33 +2121,33 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
@@ -2078,8 +2169,14 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,22 +2261,28 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>-100</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-200</v>
       </c>
       <c r="H26" s="3">
         <v>-100</v>
@@ -2188,50 +2291,50 @@
         <v>-100</v>
       </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>-2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-400</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-100</v>
       </c>
       <c r="S26" s="3">
         <v>-400</v>
       </c>
       <c r="T26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>100</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
       <c r="Y26" s="3">
         <v>0</v>
       </c>
@@ -2247,25 +2350,31 @@
       <c r="AC26" s="3">
         <v>0</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>-100</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-200</v>
       </c>
       <c r="H27" s="3">
         <v>-100</v>
@@ -2274,50 +2383,50 @@
         <v>-100</v>
       </c>
       <c r="J27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>-2500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-400</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-100</v>
       </c>
       <c r="S27" s="3">
         <v>-400</v>
       </c>
       <c r="T27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>100</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
       <c r="Y27" s="3">
         <v>0</v>
       </c>
@@ -2333,11 +2442,17 @@
       <c r="AC27" s="3">
         <v>0</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,43 +2537,49 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>1900</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>100</v>
-      </c>
-      <c r="F29" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>-200</v>
       </c>
       <c r="I29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K29" s="3">
         <v>-400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>-100</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2508,8 +2629,14 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2721,14 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,53 +2813,59 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
         <v>0</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
+      <c r="E32" s="3">
+        <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2763,77 +2902,83 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>1800</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-300</v>
-      </c>
       <c r="G33" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3">
         <v>-300</v>
       </c>
       <c r="I33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-400</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-100</v>
       </c>
       <c r="S33" s="3">
         <v>-400</v>
       </c>
       <c r="T33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>100</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="3">
         <v>0</v>
       </c>
@@ -2849,11 +2994,17 @@
       <c r="AC33" s="3">
         <v>0</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,74 +3089,80 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>1800</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-300</v>
-      </c>
       <c r="G35" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
         <v>-300</v>
       </c>
       <c r="I35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-400</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-100</v>
       </c>
       <c r="S35" s="3">
         <v>-400</v>
       </c>
       <c r="T35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>100</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="3">
         <v>0</v>
       </c>
@@ -3021,102 +3178,114 @@
       <c r="AC35" s="3">
         <v>0</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43312</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43220</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43131</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42947</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3316,10 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,74 +3350,76 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
+        <v>100</v>
+      </c>
+      <c r="G41" s="3">
         <v>900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
-      </c>
-      <c r="G41" s="3">
-        <v>100</v>
-      </c>
-      <c r="H41" s="3">
-        <v>100</v>
       </c>
       <c r="I41" s="3">
         <v>100</v>
       </c>
       <c r="J41" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="K41" s="3">
         <v>100</v>
       </c>
       <c r="L41" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="M41" s="3">
         <v>100</v>
       </c>
       <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
+        <v>100</v>
+      </c>
+      <c r="P41" s="3">
         <v>600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>500</v>
-      </c>
-      <c r="P41" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>200</v>
       </c>
       <c r="R41" s="3">
         <v>300</v>
       </c>
       <c r="S41" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="T41" s="3">
         <v>300</v>
       </c>
       <c r="U41" s="3">
+        <v>600</v>
+      </c>
+      <c r="V41" s="3">
+        <v>300</v>
+      </c>
+      <c r="W41" s="3">
         <v>400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>200</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
       <c r="Y41" s="3">
         <v>0</v>
       </c>
@@ -3262,11 +3435,17 @@
       <c r="AC41" s="3">
         <v>0</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3351,25 +3530,31 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2800</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
+        <v>3300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3000</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
@@ -3386,36 +3571,36 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>100</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3425,11 +3610,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -3437,52 +3622,58 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3">
         <v>100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1300</v>
-      </c>
-      <c r="J44" s="3">
-        <v>200</v>
-      </c>
-      <c r="K44" s="3">
-        <v>200</v>
       </c>
       <c r="L44" s="3">
         <v>200</v>
       </c>
       <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="N44" s="3">
+        <v>200</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3523,61 +3714,67 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="E45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="3">
         <v>1100</v>
       </c>
-      <c r="F45" s="3">
-        <v>1200</v>
-      </c>
       <c r="G45" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>900</v>
+      </c>
+      <c r="J45" s="3">
         <v>400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>300</v>
       </c>
       <c r="K45" s="3">
         <v>300</v>
       </c>
       <c r="L45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M45" s="3">
         <v>300</v>
       </c>
       <c r="N45" s="3">
+        <v>200</v>
+      </c>
+      <c r="O45" s="3">
+        <v>300</v>
+      </c>
+      <c r="P45" s="3">
         <v>400</v>
-      </c>
-      <c r="O45" s="3">
-        <v>100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>200</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
       </c>
       <c r="R45" s="3">
+        <v>200</v>
+      </c>
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
       <c r="T45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -3606,77 +3803,83 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F46" s="3">
         <v>4300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1300</v>
-      </c>
-      <c r="K46" s="3">
-        <v>500</v>
-      </c>
-      <c r="L46" s="3">
-        <v>400</v>
       </c>
       <c r="M46" s="3">
         <v>500</v>
       </c>
       <c r="N46" s="3">
+        <v>400</v>
+      </c>
+      <c r="O46" s="3">
+        <v>500</v>
+      </c>
+      <c r="P46" s="3">
         <v>1000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>200</v>
       </c>
-      <c r="W46" s="3">
-        <v>0</v>
-      </c>
-      <c r="X46" s="3">
-        <v>0</v>
-      </c>
       <c r="Y46" s="3">
         <v>0</v>
       </c>
@@ -3692,22 +3895,28 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
       </c>
       <c r="G47" s="3">
         <v>0</v>
@@ -3722,25 +3931,25 @@
         <v>0</v>
       </c>
       <c r="K47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M47" s="3">
         <v>100</v>
       </c>
       <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="O47" s="3">
+        <v>100</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3781,8 +3990,14 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3793,34 +4008,34 @@
         <v>0</v>
       </c>
       <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
         <v>800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>900</v>
-      </c>
-      <c r="N48" s="3">
-        <v>200</v>
-      </c>
-      <c r="O48" s="3">
-        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>200</v>
@@ -3829,22 +4044,22 @@
         <v>200</v>
       </c>
       <c r="R48" s="3">
+        <v>200</v>
+      </c>
+      <c r="S48" s="3">
+        <v>200</v>
+      </c>
+      <c r="T48" s="3">
         <v>300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>300</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3">
         <v>0</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
@@ -3861,14 +4076,20 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3890,11 +4111,11 @@
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -3908,11 +4129,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3953,8 +4174,14 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4266,14 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,16 +4358,22 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E52" s="3">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -4146,7 +4385,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
@@ -4160,17 +4399,17 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -4190,17 +4429,17 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
@@ -4211,8 +4450,14 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,74 +4542,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F54" s="3">
         <v>4300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2100</v>
-      </c>
-      <c r="K54" s="3">
-        <v>1500</v>
-      </c>
-      <c r="L54" s="3">
-        <v>1600</v>
       </c>
       <c r="M54" s="3">
         <v>1500</v>
       </c>
       <c r="N54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P54" s="3">
         <v>1300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>200</v>
       </c>
-      <c r="W54" s="3">
-        <v>0</v>
-      </c>
-      <c r="X54" s="3">
-        <v>0</v>
-      </c>
       <c r="Y54" s="3">
         <v>0</v>
       </c>
@@ -4380,11 +4631,17 @@
       <c r="AC54" s="3">
         <v>0</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4672,10 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,8 +4706,10 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4459,32 +4720,32 @@
         <v>0</v>
       </c>
       <c r="F57" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G57" s="3">
         <v>0</v>
       </c>
       <c r="H57" s="3">
+        <v>200</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
       <c r="O57" s="3">
         <v>0</v>
       </c>
@@ -4500,32 +4761,32 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
+        <v>0</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
+      <c r="Y57" s="3">
+        <v>0</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>0</v>
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC57" s="3">
         <v>0</v>
@@ -4533,31 +4794,37 @@
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4565,18 +4832,18 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
         <v>200</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4586,11 +4853,11 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -4598,11 +4865,11 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4616,79 +4883,85 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F59" s="3">
         <v>2000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3900</v>
       </c>
-      <c r="G59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J59" s="3">
         <v>2400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>600</v>
-      </c>
-      <c r="M59" s="3">
-        <v>500</v>
       </c>
       <c r="N59" s="3">
         <v>600</v>
       </c>
       <c r="O59" s="3">
+        <v>500</v>
+      </c>
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
+        <v>600</v>
+      </c>
+      <c r="R59" s="3">
         <v>300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>100</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
+      <c r="Y59" s="3">
+        <v>0</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
@@ -4696,83 +4969,89 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB59" s="3">
-        <v>0</v>
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F60" s="3">
         <v>2000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J60" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N60" s="3">
+        <v>700</v>
+      </c>
+      <c r="O60" s="3">
+        <v>500</v>
+      </c>
+      <c r="P60" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>600</v>
+      </c>
+      <c r="R60" s="3">
+        <v>300</v>
+      </c>
+      <c r="S60" s="3">
         <v>1100</v>
       </c>
-      <c r="H60" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I60" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="T60" s="3">
         <v>1000</v>
       </c>
-      <c r="L60" s="3">
-        <v>700</v>
-      </c>
-      <c r="M60" s="3">
-        <v>500</v>
-      </c>
-      <c r="N60" s="3">
-        <v>800</v>
-      </c>
-      <c r="O60" s="3">
-        <v>600</v>
-      </c>
-      <c r="P60" s="3">
+      <c r="U60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V60" s="3">
         <v>300</v>
       </c>
-      <c r="Q60" s="3">
-        <v>1100</v>
-      </c>
-      <c r="R60" s="3">
-        <v>1000</v>
-      </c>
-      <c r="S60" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T60" s="3">
+      <c r="W60" s="3">
         <v>300</v>
       </c>
-      <c r="U60" s="3">
-        <v>300</v>
-      </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>100</v>
       </c>
-      <c r="W60" s="3">
-        <v>0</v>
-      </c>
-      <c r="X60" s="3">
-        <v>0</v>
-      </c>
       <c r="Y60" s="3">
         <v>0</v>
       </c>
@@ -4788,11 +5067,17 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4803,10 +5088,10 @@
         <v>600</v>
       </c>
       <c r="F61" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H61" s="3">
         <v>100</v>
@@ -4836,10 +5121,10 @@
         <v>100</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -4877,52 +5162,58 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>2300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3300</v>
       </c>
       <c r="H62" s="3">
         <v>300</v>
       </c>
       <c r="I62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J62" s="3">
         <v>300</v>
       </c>
-      <c r="J62" s="3">
-        <v>400</v>
-      </c>
       <c r="K62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L62" s="3">
         <v>400</v>
       </c>
       <c r="M62" s="3">
+        <v>400</v>
+      </c>
+      <c r="N62" s="3">
+        <v>400</v>
+      </c>
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -4963,8 +5254,14 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5346,14 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5438,14 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,74 +5530,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F66" s="3">
         <v>2700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>100</v>
       </c>
-      <c r="W66" s="3">
-        <v>0</v>
-      </c>
-      <c r="X66" s="3">
-        <v>0</v>
-      </c>
       <c r="Y66" s="3">
         <v>0</v>
       </c>
@@ -5304,11 +5619,17 @@
       <c r="AC66" s="3">
         <v>0</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5660,10 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5748,14 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5840,14 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5932,14 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,71 +6024,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="G72" s="3">
         <v>-5100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-5100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-4800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-4600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-4300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-4000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-3900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-3400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-3000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-2200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-1300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>200</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
-      <c r="W72" s="3">
-        <v>0</v>
-      </c>
       <c r="X72" s="3">
         <v>0</v>
       </c>
@@ -5766,11 +6113,17 @@
       <c r="AC72" s="3">
         <v>0</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6208,14 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6300,14 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,74 +6392,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G76" s="3">
         <v>-200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-1400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-1000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-100</v>
       </c>
-      <c r="K76" s="3">
-        <v>0</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
+        <v>0</v>
+      </c>
+      <c r="N76" s="3">
         <v>400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>100</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
-      </c>
-      <c r="X76" s="3">
-        <v>0</v>
-      </c>
       <c r="Y76" s="3">
         <v>0</v>
       </c>
@@ -6110,11 +6481,17 @@
       <c r="AC76" s="3">
         <v>0</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,165 +6576,177 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43312</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43220</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43131</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42947</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>1800</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-300</v>
-      </c>
       <c r="G81" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
         <v>-300</v>
       </c>
       <c r="I81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-400</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-100</v>
       </c>
       <c r="S81" s="3">
         <v>-400</v>
       </c>
       <c r="T81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>100</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3">
         <v>0</v>
       </c>
@@ -6373,11 +6762,17 @@
       <c r="AC81" s="3">
         <v>0</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,8 +6803,10 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6461,14 +6858,14 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -6485,17 +6882,23 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6983,14 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +7075,14 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +7167,14 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7259,14 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,71 +7351,77 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-400</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-100</v>
       </c>
       <c r="P89" s="3">
         <v>-500</v>
       </c>
       <c r="Q89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>300</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3">
         <v>100</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
         <v>0</v>
       </c>
@@ -7007,11 +7440,17 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,13 +7481,15 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
@@ -7057,7 +7498,7 @@
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -7072,14 +7513,14 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7092,14 +7533,14 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
@@ -7113,11 +7554,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -7125,11 +7566,17 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7661,14 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,8 +7753,14 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7312,37 +7771,37 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -7350,20 +7809,20 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -7383,11 +7842,17 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7883,10 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7504,8 +7971,14 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +8063,14 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +8155,14 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,46 +8247,52 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>900</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>600</v>
-      </c>
-      <c r="O100" s="3">
-        <v>300</v>
       </c>
       <c r="P100" s="3">
         <v>600</v>
@@ -7810,26 +8301,26 @@
         <v>300</v>
       </c>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="S100" s="3">
+        <v>300</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
@@ -7845,11 +8336,17 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7901,11 +8398,11 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
@@ -7919,11 +8416,11 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -7934,74 +8431,80 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>800</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-100</v>
       </c>
       <c r="M102" s="3">
         <v>-400</v>
       </c>
       <c r="N102" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="O102" s="3">
-        <v>200</v>
+        <v>-400</v>
       </c>
       <c r="P102" s="3">
         <v>100</v>
       </c>
       <c r="Q102" s="3">
+        <v>200</v>
+      </c>
+      <c r="R102" s="3">
+        <v>100</v>
+      </c>
+      <c r="S102" s="3">
         <v>-300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>400</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
         <v>0</v>
       </c>
@@ -8017,7 +8520,13 @@
       <c r="AC102" s="3">
         <v>0</v>
       </c>
-      <c r="AD102" s="3" t="s">
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VIVC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VIVC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>VIVC</t>
   </si>
@@ -656,157 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43677</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43585</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43496</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43404</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43312</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43220</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43131</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43039</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42947</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1800</v>
-      </c>
-      <c r="E8" s="3">
-        <v>800</v>
       </c>
       <c r="F8" s="3">
         <v>800</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
+      <c r="G8" s="3">
+        <v>800</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -821,16 +825,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>200</v>
-      </c>
-      <c r="N8" s="3">
-        <v>100</v>
       </c>
       <c r="O8" s="3">
         <v>100</v>
       </c>
       <c r="P8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -839,26 +843,26 @@
         <v>0</v>
       </c>
       <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>100</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
       <c r="Z8" s="3">
         <v>0</v>
       </c>
@@ -880,22 +884,25 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E9" s="3">
         <v>600</v>
-      </c>
-      <c r="E9" s="3">
-        <v>700</v>
       </c>
       <c r="F9" s="3">
         <v>700</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+      <c r="G9" s="3">
+        <v>700</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -903,8 +910,8 @@
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J9" s="3">
-        <v>0</v>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -913,34 +920,34 @@
         <v>0</v>
       </c>
       <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
       <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>0</v>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R9" s="3">
         <v>0</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T9" s="3">
-        <v>0</v>
+      <c r="S9" s="3">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U9" s="3">
         <v>0</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
+      <c r="V9" s="3">
+        <v>0</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
@@ -960,8 +967,8 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC9" s="3">
-        <v>0</v>
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD9" s="3">
         <v>0</v>
@@ -969,25 +976,28 @@
       <c r="AE9" s="3">
         <v>0</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>900</v>
+      </c>
+      <c r="E10" s="3">
         <v>1200</v>
-      </c>
-      <c r="E10" s="3">
-        <v>100</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="G10" s="3">
+        <v>100</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -995,8 +1005,8 @@
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -1005,35 +1015,35 @@
         <v>0</v>
       </c>
       <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
         <v>-200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>0</v>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R10" s="3">
         <v>0</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3">
         <v>100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>400</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1052,8 +1062,8 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC10" s="3">
-        <v>0</v>
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD10" s="3">
         <v>0</v>
@@ -1061,11 +1071,14 @@
       <c r="AE10" s="3">
         <v>0</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1293,8 +1313,8 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1315,22 +1335,22 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1800</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
@@ -1338,12 +1358,12 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,8 +1379,8 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,28 +1523,29 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1100</v>
-      </c>
-      <c r="E17" s="3">
-        <v>800</v>
       </c>
       <c r="F17" s="3">
         <v>800</v>
       </c>
       <c r="G17" s="3">
+        <v>800</v>
+      </c>
+      <c r="H17" s="3">
         <v>100</v>
       </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
       <c r="I17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3">
         <v>100</v>
@@ -1527,38 +1554,38 @@
         <v>100</v>
       </c>
       <c r="L17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
         <v>3000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>800</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
       <c r="W17" s="3">
         <v>0</v>
       </c>
@@ -1586,31 +1613,34 @@
       <c r="AE17" s="3">
         <v>0</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>500</v>
+      </c>
+      <c r="E18" s="3">
         <v>700</v>
       </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
       <c r="F18" s="3">
         <v>0</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0</v>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
         <v>-100</v>
@@ -1619,47 +1649,47 @@
         <v>-100</v>
       </c>
       <c r="L18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
         <v>-2800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-900</v>
       </c>
       <c r="P18" s="3">
         <v>-900</v>
       </c>
       <c r="Q18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="R18" s="3">
         <v>-400</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-300</v>
       </c>
       <c r="S18" s="3">
         <v>-300</v>
       </c>
       <c r="T18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>100</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
       <c r="Z18" s="3">
         <v>0</v>
       </c>
@@ -1678,11 +1708,14 @@
       <c r="AE18" s="3">
         <v>0</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1748,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1729,15 +1763,15 @@
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1748,23 +1782,23 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>200</v>
       </c>
       <c r="O20" s="3">
+        <v>200</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1804,55 +1838,58 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>400</v>
+      </c>
+      <c r="E21" s="3">
         <v>800</v>
       </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
       <c r="F21" s="3">
         <v>0</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-100</v>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I21" s="3">
         <v>-100</v>
       </c>
       <c r="J21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>-100</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
       <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-2500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-400</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-900</v>
       </c>
       <c r="P21" s="3">
         <v>-900</v>
       </c>
       <c r="Q21" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="R21" s="3">
         <v>-300</v>
@@ -1861,23 +1898,23 @@
         <v>-300</v>
       </c>
       <c r="T21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U21" s="3">
         <v>-100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-300</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>100</v>
       </c>
-      <c r="Y21" s="3">
-        <v>0</v>
-      </c>
       <c r="Z21" s="3">
         <v>0</v>
       </c>
@@ -1890,8 +1927,8 @@
       <c r="AC21" s="3">
         <v>0</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
+      <c r="AD21" s="3">
+        <v>0</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
@@ -1899,8 +1936,11 @@
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1958,8 +1998,8 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -1976,8 +2016,8 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -1991,22 +2031,25 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>400</v>
+      </c>
+      <c r="E23" s="3">
         <v>800</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
       <c r="F23" s="3">
         <v>0</v>
       </c>
       <c r="G23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3">
         <v>-100</v>
@@ -2021,47 +2064,47 @@
         <v>-100</v>
       </c>
       <c r="L23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>-2600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-400</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-900</v>
       </c>
       <c r="P23" s="3">
         <v>-900</v>
       </c>
       <c r="Q23" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="R23" s="3">
         <v>-300</v>
       </c>
       <c r="S23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T23" s="3">
         <v>-400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>100</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
       <c r="Z23" s="3">
         <v>0</v>
       </c>
@@ -2080,20 +2123,23 @@
       <c r="AE23" s="3">
         <v>0</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -2127,14 +2173,14 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -2143,13 +2189,13 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W24" s="3">
         <v>100</v>
       </c>
       <c r="X24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -2175,8 +2221,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,22 +2316,25 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>400</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
       <c r="F26" s="3">
         <v>0</v>
       </c>
       <c r="G26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
         <v>-100</v>
@@ -2297,47 +2349,47 @@
         <v>-100</v>
       </c>
       <c r="L26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>-2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-400</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-900</v>
       </c>
       <c r="P26" s="3">
         <v>-900</v>
       </c>
       <c r="Q26" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="R26" s="3">
         <v>-300</v>
       </c>
       <c r="S26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>100</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
-      </c>
       <c r="Z26" s="3">
         <v>0</v>
       </c>
@@ -2356,25 +2408,28 @@
       <c r="AE26" s="3">
         <v>0</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>400</v>
+      </c>
+      <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
       <c r="F27" s="3">
         <v>0</v>
       </c>
       <c r="G27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3">
         <v>-100</v>
@@ -2389,47 +2444,47 @@
         <v>-100</v>
       </c>
       <c r="L27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>-2500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-400</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-900</v>
       </c>
       <c r="P27" s="3">
         <v>-900</v>
       </c>
       <c r="Q27" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="R27" s="3">
         <v>-300</v>
       </c>
       <c r="S27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T27" s="3">
         <v>-400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>100</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
       <c r="Z27" s="3">
         <v>0</v>
       </c>
@@ -2448,11 +2503,14 @@
       <c r="AE27" s="3">
         <v>0</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2555,34 +2616,34 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>1900</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-400</v>
-      </c>
-      <c r="L29" s="3">
-        <v>-100</v>
       </c>
       <c r="M29" s="3">
         <v>-100</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="N29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2886,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2833,15 +2903,15 @@
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2852,23 +2922,23 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>-200</v>
       </c>
       <c r="O32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2908,80 +2978,83 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>400</v>
+      </c>
+      <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>1800</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-400</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-900</v>
       </c>
       <c r="P33" s="3">
         <v>-900</v>
       </c>
       <c r="Q33" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="R33" s="3">
         <v>-300</v>
       </c>
       <c r="S33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T33" s="3">
         <v>-400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-400</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>100</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
       <c r="Z33" s="3">
         <v>0</v>
       </c>
@@ -3000,11 +3073,14 @@
       <c r="AE33" s="3">
         <v>0</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,77 +3171,80 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>400</v>
+      </c>
+      <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>1800</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-400</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-900</v>
       </c>
       <c r="P35" s="3">
         <v>-900</v>
       </c>
       <c r="Q35" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="R35" s="3">
         <v>-300</v>
       </c>
       <c r="S35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T35" s="3">
         <v>-400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-400</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>100</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
       <c r="Z35" s="3">
         <v>0</v>
       </c>
@@ -3184,108 +3263,114 @@
       <c r="AE35" s="3">
         <v>0</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43677</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43585</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43496</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43404</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43312</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43220</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43131</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43039</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42947</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,28 +3438,29 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F41" s="3">
         <v>100</v>
       </c>
       <c r="G41" s="3">
+        <v>100</v>
+      </c>
+      <c r="H41" s="3">
         <v>900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
-      </c>
-      <c r="I41" s="3">
-        <v>100</v>
       </c>
       <c r="J41" s="3">
         <v>100</v>
@@ -3382,47 +3469,47 @@
         <v>100</v>
       </c>
       <c r="L41" s="3">
+        <v>100</v>
+      </c>
+      <c r="M41" s="3">
         <v>800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
       <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3">
         <v>100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>200</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
       <c r="Z41" s="3">
         <v>0</v>
       </c>
@@ -3441,11 +3528,14 @@
       <c r="AE41" s="3">
         <v>0</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,29 +3626,32 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E43" s="3">
         <v>3300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
       <c r="J43" s="3">
         <v>0</v>
       </c>
@@ -3577,33 +3670,33 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
+      <c r="P43" s="3">
+        <v>0</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3">
         <v>200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
       <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
         <v>200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>100</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3616,8 +3709,8 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -3628,37 +3721,40 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>0</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3">
         <v>100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>900</v>
-      </c>
-      <c r="I44" s="3">
-        <v>1500</v>
       </c>
       <c r="J44" s="3">
         <v>1500</v>
       </c>
       <c r="K44" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L44" s="3">
         <v>1300</v>
-      </c>
-      <c r="L44" s="3">
-        <v>200</v>
       </c>
       <c r="M44" s="3">
         <v>200</v>
@@ -3667,16 +3763,16 @@
         <v>200</v>
       </c>
       <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -3720,34 +3816,37 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1000</v>
       </c>
       <c r="H45" s="3">
         <v>1000</v>
       </c>
       <c r="I45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J45" s="3">
         <v>900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
-      </c>
-      <c r="K45" s="3">
-        <v>300</v>
       </c>
       <c r="L45" s="3">
         <v>300</v>
@@ -3756,28 +3855,28 @@
         <v>300</v>
       </c>
       <c r="N45" s="3">
+        <v>300</v>
+      </c>
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
-      </c>
-      <c r="S45" s="3">
-        <v>100</v>
       </c>
       <c r="T45" s="3">
         <v>100</v>
       </c>
       <c r="U45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
@@ -3809,80 +3908,83 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4100</v>
+        <v>4900</v>
       </c>
       <c r="E46" s="3">
         <v>4100</v>
       </c>
       <c r="F46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G46" s="3">
         <v>4300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>600</v>
       </c>
       <c r="R46" s="3">
         <v>600</v>
       </c>
       <c r="S46" s="3">
+        <v>600</v>
+      </c>
+      <c r="T46" s="3">
         <v>300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>500</v>
-      </c>
-      <c r="U46" s="3">
-        <v>600</v>
       </c>
       <c r="V46" s="3">
         <v>600</v>
       </c>
       <c r="W46" s="3">
+        <v>600</v>
+      </c>
+      <c r="X46" s="3">
         <v>500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>200</v>
       </c>
-      <c r="Y46" s="3">
-        <v>0</v>
-      </c>
       <c r="Z46" s="3">
         <v>0</v>
       </c>
@@ -3901,11 +4003,14 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3937,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N47" s="3">
         <v>100</v>
@@ -3946,13 +4051,13 @@
         <v>100</v>
       </c>
       <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3996,8 +4101,11 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4014,31 +4122,31 @@
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
         <v>800</v>
       </c>
       <c r="J48" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K48" s="3">
         <v>700</v>
       </c>
       <c r="L48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="M48" s="3">
         <v>800</v>
       </c>
       <c r="N48" s="3">
+        <v>800</v>
+      </c>
+      <c r="O48" s="3">
         <v>1000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>900</v>
-      </c>
-      <c r="P48" s="3">
-        <v>200</v>
       </c>
       <c r="Q48" s="3">
         <v>200</v>
@@ -4050,19 +4158,19 @@
         <v>200</v>
       </c>
       <c r="T48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U48" s="3">
         <v>300</v>
       </c>
       <c r="V48" s="3">
-        <v>0</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X48" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -4082,14 +4190,17 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
+      <c r="AE48" s="3">
+        <v>0</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4117,8 +4228,8 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -4135,8 +4246,8 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,32 +4481,35 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
       <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
         <v>2700</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>2700</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
@@ -4405,14 +4525,14 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -4435,14 +4555,14 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
+      <c r="Z52" s="3">
+        <v>0</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,77 +4671,80 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4100</v>
+        <v>4900</v>
       </c>
       <c r="E54" s="3">
         <v>4100</v>
       </c>
       <c r="F54" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G54" s="3">
         <v>4300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5500</v>
-      </c>
-      <c r="H54" s="3">
-        <v>3200</v>
       </c>
       <c r="I54" s="3">
         <v>3200</v>
       </c>
       <c r="J54" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K54" s="3">
         <v>2600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>900</v>
       </c>
       <c r="R54" s="3">
         <v>900</v>
       </c>
       <c r="S54" s="3">
+        <v>900</v>
+      </c>
+      <c r="T54" s="3">
         <v>600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>200</v>
       </c>
-      <c r="Y54" s="3">
-        <v>0</v>
-      </c>
       <c r="Z54" s="3">
         <v>0</v>
       </c>
@@ -4637,11 +4763,14 @@
       <c r="AE54" s="3">
         <v>0</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,13 +4838,14 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
@@ -4726,29 +4857,29 @@
         <v>0</v>
       </c>
       <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
       <c r="J57" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K57" s="3">
         <v>600</v>
       </c>
       <c r="L57" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
       <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
@@ -4767,8 +4898,8 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
+      <c r="V57" s="3">
+        <v>0</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
@@ -4776,11 +4907,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>0</v>
       </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
@@ -4788,8 +4919,8 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD57" s="3">
         <v>0</v>
@@ -4800,8 +4931,11 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4817,17 +4951,17 @@
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -4838,15 +4972,15 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4859,8 +4993,8 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
+      <c r="V58" s="3">
+        <v>0</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
@@ -4871,8 +5005,8 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4889,82 +5023,85 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>500</v>
-      </c>
-      <c r="P59" s="3">
-        <v>600</v>
       </c>
       <c r="Q59" s="3">
         <v>600</v>
       </c>
       <c r="R59" s="3">
+        <v>600</v>
+      </c>
+      <c r="S59" s="3">
         <v>300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1100</v>
-      </c>
-      <c r="T59" s="3">
-        <v>1000</v>
       </c>
       <c r="U59" s="3">
         <v>1000</v>
       </c>
       <c r="V59" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="W59" s="3">
         <v>300</v>
       </c>
       <c r="X59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y59" s="3">
         <v>100</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
+      <c r="Z59" s="3">
+        <v>0</v>
       </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
@@ -4975,86 +5112,89 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>0</v>
       </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1100</v>
-      </c>
-      <c r="T60" s="3">
-        <v>1000</v>
       </c>
       <c r="U60" s="3">
         <v>1000</v>
       </c>
       <c r="V60" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="W60" s="3">
         <v>300</v>
       </c>
       <c r="X60" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y60" s="3">
         <v>100</v>
       </c>
-      <c r="Y60" s="3">
-        <v>0</v>
-      </c>
       <c r="Z60" s="3">
         <v>0</v>
       </c>
@@ -5073,11 +5213,14 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5094,7 +5237,7 @@
         <v>600</v>
       </c>
       <c r="H61" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="I61" s="3">
         <v>100</v>
@@ -5127,7 +5270,7 @@
         <v>100</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -5168,37 +5311,40 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
       </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>2300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>300</v>
       </c>
       <c r="K62" s="3">
         <v>300</v>
       </c>
       <c r="L62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M62" s="3">
         <v>400</v>
@@ -5207,16 +5353,16 @@
         <v>400</v>
       </c>
       <c r="O62" s="3">
+        <v>400</v>
+      </c>
+      <c r="P62" s="3">
         <v>500</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,77 +5691,80 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1500</v>
-      </c>
-      <c r="N66" s="3">
-        <v>1100</v>
       </c>
       <c r="O66" s="3">
         <v>1100</v>
       </c>
       <c r="P66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q66" s="3">
         <v>1000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1200</v>
-      </c>
-      <c r="T66" s="3">
-        <v>1100</v>
       </c>
       <c r="U66" s="3">
         <v>1100</v>
       </c>
       <c r="V66" s="3">
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="W66" s="3">
         <v>300</v>
       </c>
       <c r="X66" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y66" s="3">
         <v>100</v>
       </c>
-      <c r="Y66" s="3">
-        <v>0</v>
-      </c>
       <c r="Z66" s="3">
         <v>0</v>
       </c>
@@ -5625,11 +5783,14 @@
       <c r="AE66" s="3">
         <v>0</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,73 +6201,76 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2700</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-3300</v>
       </c>
       <c r="F72" s="3">
         <v>-3300</v>
       </c>
       <c r="G72" s="3">
-        <v>-5100</v>
+        <v>-3300</v>
       </c>
       <c r="H72" s="3">
         <v>-5100</v>
       </c>
       <c r="I72" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="J72" s="3">
         <v>-4800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-4600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-300</v>
-      </c>
-      <c r="V72" s="3">
-        <v>200</v>
       </c>
       <c r="W72" s="3">
         <v>200</v>
       </c>
       <c r="X72" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y72" s="3">
         <v>0</v>
@@ -6119,11 +6293,14 @@
       <c r="AE72" s="3">
         <v>0</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,77 +6581,80 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2200</v>
-      </c>
-      <c r="E76" s="3">
-        <v>1600</v>
       </c>
       <c r="F76" s="3">
         <v>1600</v>
       </c>
       <c r="G76" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H76" s="3">
         <v>-200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-100</v>
       </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
       <c r="N76" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="O76" s="3">
         <v>400</v>
       </c>
       <c r="P76" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q76" s="3">
         <v>300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>100</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
-      </c>
       <c r="Z76" s="3">
         <v>0</v>
       </c>
@@ -6487,11 +6673,14 @@
       <c r="AE76" s="3">
         <v>0</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,174 +6771,180 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43677</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43585</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43496</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43404</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43312</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43220</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43131</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43039</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42947</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>400</v>
+      </c>
+      <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>1800</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-400</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-900</v>
       </c>
       <c r="P81" s="3">
         <v>-900</v>
       </c>
       <c r="Q81" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="R81" s="3">
         <v>-300</v>
       </c>
       <c r="S81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T81" s="3">
         <v>-400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-400</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>100</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
       <c r="Z81" s="3">
         <v>0</v>
       </c>
@@ -6768,11 +6963,14 @@
       <c r="AE81" s="3">
         <v>0</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6864,11 +7063,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -6888,8 +7087,8 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,74 +7571,77 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>300</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3">
         <v>100</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
         <v>0</v>
       </c>
@@ -7446,11 +7663,14 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7519,11 +7740,11 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7539,11 +7760,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -7560,8 +7781,8 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -7572,11 +7793,14 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,13 +7986,16 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -7777,34 +8007,34 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3">
         <v>-100</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L94" s="3">
         <v>100</v>
       </c>
       <c r="M94" s="3">
+        <v>100</v>
+      </c>
+      <c r="N94" s="3">
         <v>-400</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-200</v>
       </c>
       <c r="O94" s="3">
         <v>-200</v>
       </c>
       <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -7815,17 +8045,17 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -7848,11 +8078,14 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,76 +8496,79 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
-      </c>
-      <c r="I100" s="3">
-        <v>200</v>
       </c>
       <c r="J100" s="3">
         <v>200</v>
       </c>
       <c r="K100" s="3">
+        <v>200</v>
+      </c>
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>900</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W100" s="3">
-        <v>100</v>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X100" s="3">
         <v>100</v>
       </c>
       <c r="Y100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -8342,11 +8588,14 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8404,8 +8653,8 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
@@ -8422,8 +8671,8 @@
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
@@ -8437,76 +8686,79 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>400</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W102" s="3">
-        <v>200</v>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X102" s="3">
         <v>200</v>
       </c>
       <c r="Y102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
@@ -8526,7 +8778,10 @@
       <c r="AE102" s="3">
         <v>0</v>
       </c>
-      <c r="AF102" s="3" t="s">
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VIVC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VIVC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
   <si>
     <t>VIVC</t>
   </si>
@@ -656,167 +656,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43677</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43585</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43496</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43404</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43312</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43220</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43131</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43039</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42947</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>2600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1800</v>
-      </c>
-      <c r="F8" s="3">
-        <v>800</v>
       </c>
       <c r="G8" s="3">
         <v>800</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
+      <c r="H8" s="3">
+        <v>800</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+        <v>800</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -828,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>200</v>
-      </c>
-      <c r="O8" s="3">
-        <v>100</v>
       </c>
       <c r="P8" s="3">
         <v>100</v>
       </c>
       <c r="Q8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -846,26 +849,26 @@
         <v>0</v>
       </c>
       <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <v>200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>100</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
-      </c>
       <c r="AA8" s="3">
         <v>0</v>
       </c>
@@ -887,34 +890,37 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>600</v>
-      </c>
-      <c r="F9" s="3">
-        <v>700</v>
       </c>
       <c r="G9" s="3">
         <v>700</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
+      <c r="H9" s="3">
+        <v>700</v>
+      </c>
+      <c r="I9" s="3">
+        <v>700</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3">
-        <v>0</v>
+      <c r="K9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L9" s="3">
         <v>0</v>
@@ -923,34 +929,34 @@
         <v>0</v>
       </c>
       <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
       <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
         <v>200</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3">
-        <v>0</v>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S9" s="3">
         <v>0</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U9" s="3">
-        <v>0</v>
+      <c r="T9" s="3">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V9" s="3">
         <v>0</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
+      <c r="W9" s="3">
+        <v>0</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
@@ -970,8 +976,8 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD9" s="3">
-        <v>0</v>
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE9" s="3">
         <v>0</v>
@@ -979,37 +985,40 @@
       <c r="AF9" s="3">
         <v>0</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>900</v>
+        <v>-100</v>
       </c>
       <c r="E10" s="3">
+        <v>800</v>
+      </c>
+      <c r="F10" s="3">
         <v>1200</v>
-      </c>
-      <c r="F10" s="3">
-        <v>100</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
+      <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>100</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
+      <c r="K10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
@@ -1018,35 +1027,35 @@
         <v>0</v>
       </c>
       <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
         <v>-200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3">
-        <v>0</v>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S10" s="3">
         <v>0</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3">
         <v>100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>400</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1065,8 +1074,8 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD10" s="3">
-        <v>0</v>
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE10" s="3">
         <v>0</v>
@@ -1074,11 +1083,14 @@
       <c r="AF10" s="3">
         <v>0</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1316,17 +1335,17 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1338,22 +1357,22 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1800</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
@@ -1361,12 +1380,12 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1382,8 +1401,8 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1397,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,28 +1549,29 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1100</v>
-      </c>
-      <c r="F17" s="3">
-        <v>800</v>
       </c>
       <c r="G17" s="3">
         <v>800</v>
       </c>
       <c r="H17" s="3">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="I17" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J17" s="3">
         <v>100</v>
@@ -1557,38 +1583,38 @@
         <v>100</v>
       </c>
       <c r="M17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
         <v>3000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>800</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
       <c r="X17" s="3">
         <v>0</v>
       </c>
@@ -1616,28 +1642,31 @@
       <c r="AF17" s="3">
         <v>0</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>500</v>
+        <v>-600</v>
       </c>
       <c r="E18" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
+      <c r="H18" s="3">
+        <v>0</v>
       </c>
       <c r="I18" s="3">
         <v>0</v>
@@ -1652,47 +1681,47 @@
         <v>-100</v>
       </c>
       <c r="M18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>-2800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-500</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-900</v>
       </c>
       <c r="Q18" s="3">
         <v>-900</v>
       </c>
       <c r="R18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="S18" s="3">
         <v>-400</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-300</v>
       </c>
       <c r="T18" s="3">
         <v>-300</v>
       </c>
       <c r="U18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>100</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
       <c r="AA18" s="3">
         <v>0</v>
       </c>
@@ -1711,11 +1740,14 @@
       <c r="AF18" s="3">
         <v>0</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1781,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1760,17 +1793,17 @@
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1785,23 +1818,23 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>200</v>
       </c>
       <c r="P20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1841,58 +1874,61 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E21" s="3">
         <v>400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>800</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
       <c r="G21" s="3">
         <v>0</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+      <c r="H21" s="3">
+        <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>-100</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
         <v>-100</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
         <v>-2500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-400</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-900</v>
       </c>
       <c r="Q21" s="3">
         <v>-900</v>
       </c>
       <c r="R21" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="S21" s="3">
         <v>-300</v>
@@ -1901,23 +1937,23 @@
         <v>-300</v>
       </c>
       <c r="U21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V21" s="3">
         <v>-100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-300</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>100</v>
       </c>
-      <c r="Z21" s="3">
-        <v>0</v>
-      </c>
       <c r="AA21" s="3">
         <v>0</v>
       </c>
@@ -1930,8 +1966,8 @@
       <c r="AD21" s="3">
         <v>0</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
+      <c r="AE21" s="3">
+        <v>0</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
@@ -1939,8 +1975,11 @@
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2001,8 +2040,8 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
@@ -2019,8 +2058,8 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2034,28 +2073,31 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E23" s="3">
         <v>400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>800</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
       <c r="G23" s="3">
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3">
         <v>-100</v>
@@ -2067,47 +2109,47 @@
         <v>-100</v>
       </c>
       <c r="M23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>-2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-400</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-900</v>
       </c>
       <c r="Q23" s="3">
         <v>-900</v>
       </c>
       <c r="R23" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="S23" s="3">
         <v>-300</v>
       </c>
       <c r="T23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U23" s="3">
         <v>-400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>100</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
       <c r="AA23" s="3">
         <v>0</v>
       </c>
@@ -2126,34 +2168,37 @@
       <c r="AF23" s="3">
         <v>0</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2176,14 +2221,14 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -2192,13 +2237,13 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
       </c>
       <c r="Y24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -2224,8 +2269,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,28 +2367,31 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E26" s="3">
         <v>400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3">
         <v>-100</v>
@@ -2352,47 +2403,47 @@
         <v>-100</v>
       </c>
       <c r="M26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>-2600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-400</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-900</v>
       </c>
       <c r="Q26" s="3">
         <v>-900</v>
       </c>
       <c r="R26" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="S26" s="3">
         <v>-300</v>
       </c>
       <c r="T26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
       <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>100</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
       <c r="AA26" s="3">
         <v>0</v>
       </c>
@@ -2411,34 +2462,37 @@
       <c r="AF26" s="3">
         <v>0</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E27" s="3">
         <v>400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>600</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>-100</v>
+        <v>1800</v>
       </c>
       <c r="I27" s="3">
-        <v>-100</v>
+        <v>1800</v>
       </c>
       <c r="J27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K27" s="3">
         <v>-100</v>
@@ -2447,47 +2501,47 @@
         <v>-100</v>
       </c>
       <c r="M27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>-2500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-400</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-900</v>
       </c>
       <c r="Q27" s="3">
         <v>-900</v>
       </c>
       <c r="R27" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="S27" s="3">
         <v>-300</v>
       </c>
       <c r="T27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U27" s="3">
         <v>-400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-400</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
       <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>100</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
       <c r="AA27" s="3">
         <v>0</v>
       </c>
@@ -2506,11 +2560,14 @@
       <c r="AF27" s="3">
         <v>0</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2619,34 +2679,34 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>1900</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J29" s="3">
         <v>100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L29" s="3">
         <v>-200</v>
       </c>
-      <c r="J29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K29" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-400</v>
-      </c>
-      <c r="M29" s="3">
-        <v>-100</v>
       </c>
       <c r="N29" s="3">
         <v>-100</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="O29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2699,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +2955,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2900,17 +2969,17 @@
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2925,23 +2994,23 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>-200</v>
       </c>
       <c r="P32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2981,83 +3050,86 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E33" s="3">
         <v>400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>600</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>1800</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-400</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-900</v>
       </c>
       <c r="Q33" s="3">
         <v>-900</v>
       </c>
       <c r="R33" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="S33" s="3">
         <v>-300</v>
       </c>
       <c r="T33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U33" s="3">
         <v>-400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-400</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
       <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>100</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
       <c r="AA33" s="3">
         <v>0</v>
       </c>
@@ -3076,11 +3148,14 @@
       <c r="AF33" s="3">
         <v>0</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,80 +3249,83 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E35" s="3">
         <v>400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>600</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>1800</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-400</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-900</v>
       </c>
       <c r="Q35" s="3">
         <v>-900</v>
       </c>
       <c r="R35" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="S35" s="3">
         <v>-300</v>
       </c>
       <c r="T35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U35" s="3">
         <v>-400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-400</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
       <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>100</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
       <c r="AA35" s="3">
         <v>0</v>
       </c>
@@ -3266,111 +3344,117 @@
       <c r="AF35" s="3">
         <v>0</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43677</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43585</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43496</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43404</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43312</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43220</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43131</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43039</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42947</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,31 +3524,32 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
       <c r="F41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G41" s="3">
         <v>100</v>
       </c>
       <c r="H41" s="3">
+        <v>100</v>
+      </c>
+      <c r="I41" s="3">
+        <v>100</v>
+      </c>
+      <c r="J41" s="3">
         <v>900</v>
-      </c>
-      <c r="I41" s="3">
-        <v>300</v>
-      </c>
-      <c r="J41" s="3">
-        <v>100</v>
       </c>
       <c r="K41" s="3">
         <v>100</v>
@@ -3472,47 +3558,47 @@
         <v>100</v>
       </c>
       <c r="M41" s="3">
+        <v>100</v>
+      </c>
+      <c r="N41" s="3">
         <v>800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>100</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
       <c r="P41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3">
         <v>100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
       <c r="AA41" s="3">
         <v>0</v>
       </c>
@@ -3531,16 +3617,19 @@
       <c r="AF41" s="3">
         <v>0</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -3552,13 +3641,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3629,19 +3718,22 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4200</v>
+        <v>2500</v>
       </c>
       <c r="E43" s="3">
-        <v>3300</v>
+        <v>4100</v>
       </c>
       <c r="F43" s="3">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="G43" s="3">
         <v>2900</v>
@@ -3650,56 +3742,56 @@
         <v>100</v>
       </c>
       <c r="I43" s="3">
+        <v>100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>100</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
+        <v>100</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="Y43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3">
-        <v>200</v>
-      </c>
-      <c r="X43" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3712,8 +3804,8 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE43" s="3">
         <v>0</v>
@@ -3724,40 +3816,43 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
         <v>0</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
+      <c r="E44" s="3">
+        <v>0</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3">
         <v>100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
+        <v>100</v>
+      </c>
+      <c r="J44" s="3">
         <v>800</v>
-      </c>
-      <c r="I44" s="3">
-        <v>900</v>
-      </c>
-      <c r="J44" s="3">
-        <v>1500</v>
       </c>
       <c r="K44" s="3">
         <v>1500</v>
       </c>
       <c r="L44" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M44" s="3">
         <v>1300</v>
-      </c>
-      <c r="M44" s="3">
-        <v>200</v>
       </c>
       <c r="N44" s="3">
         <v>200</v>
@@ -3766,16 +3861,16 @@
         <v>200</v>
       </c>
       <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -3819,37 +3914,40 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="F45" s="3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="H45" s="3">
-        <v>1000</v>
+        <v>2800</v>
       </c>
       <c r="I45" s="3">
-        <v>1000</v>
+        <v>2800</v>
       </c>
       <c r="J45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
-      </c>
-      <c r="L45" s="3">
-        <v>300</v>
       </c>
       <c r="M45" s="3">
         <v>300</v>
@@ -3858,28 +3956,28 @@
         <v>300</v>
       </c>
       <c r="O45" s="3">
+        <v>300</v>
+      </c>
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
-      </c>
-      <c r="T45" s="3">
-        <v>100</v>
       </c>
       <c r="U45" s="3">
         <v>100</v>
       </c>
       <c r="V45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -3911,83 +4009,86 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E46" s="3">
         <v>4900</v>
-      </c>
-      <c r="E46" s="3">
-        <v>4100</v>
       </c>
       <c r="F46" s="3">
         <v>4100</v>
       </c>
       <c r="G46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H46" s="3">
         <v>4300</v>
       </c>
-      <c r="H46" s="3">
-        <v>2800</v>
-      </c>
       <c r="I46" s="3">
-        <v>2400</v>
+        <v>4300</v>
       </c>
       <c r="J46" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K46" s="3">
         <v>500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1000</v>
-      </c>
-      <c r="R46" s="3">
-        <v>600</v>
       </c>
       <c r="S46" s="3">
         <v>600</v>
       </c>
       <c r="T46" s="3">
+        <v>600</v>
+      </c>
+      <c r="U46" s="3">
         <v>300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>500</v>
-      </c>
-      <c r="V46" s="3">
-        <v>600</v>
       </c>
       <c r="W46" s="3">
         <v>600</v>
       </c>
       <c r="X46" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y46" s="3">
         <v>500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>200</v>
       </c>
-      <c r="Z46" s="3">
-        <v>0</v>
-      </c>
       <c r="AA46" s="3">
         <v>0</v>
       </c>
@@ -4006,34 +4107,37 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4045,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="N47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O47" s="3">
         <v>100</v>
@@ -4054,13 +4158,13 @@
         <v>100</v>
       </c>
       <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -4104,8 +4208,11 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4125,31 +4232,31 @@
         <v>0</v>
       </c>
       <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3">
         <v>800</v>
-      </c>
-      <c r="J48" s="3">
-        <v>800</v>
-      </c>
-      <c r="K48" s="3">
-        <v>700</v>
       </c>
       <c r="L48" s="3">
         <v>700</v>
       </c>
       <c r="M48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="N48" s="3">
         <v>800</v>
       </c>
       <c r="O48" s="3">
+        <v>800</v>
+      </c>
+      <c r="P48" s="3">
         <v>1000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>900</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>200</v>
       </c>
       <c r="R48" s="3">
         <v>200</v>
@@ -4161,19 +4268,19 @@
         <v>200</v>
       </c>
       <c r="U48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V48" s="3">
         <v>300</v>
       </c>
       <c r="W48" s="3">
-        <v>0</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
@@ -4193,14 +4300,17 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>3</v>
+      <c r="AF48" s="3">
+        <v>0</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4231,8 +4341,8 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -4249,8 +4359,8 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -4294,8 +4404,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4600,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4495,24 +4614,24 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
         <v>2700</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>2700</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -4528,14 +4647,14 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3">
+        <v>0</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -4558,14 +4677,14 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
+      <c r="AA52" s="3">
+        <v>0</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
@@ -4579,8 +4698,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,80 +4796,83 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E54" s="3">
         <v>4900</v>
-      </c>
-      <c r="E54" s="3">
-        <v>4100</v>
       </c>
       <c r="F54" s="3">
         <v>4100</v>
       </c>
       <c r="G54" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H54" s="3">
         <v>4300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J54" s="3">
         <v>5500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3200</v>
       </c>
-      <c r="J54" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1300</v>
-      </c>
-      <c r="R54" s="3">
-        <v>900</v>
       </c>
       <c r="S54" s="3">
         <v>900</v>
       </c>
       <c r="T54" s="3">
+        <v>900</v>
+      </c>
+      <c r="U54" s="3">
         <v>600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>200</v>
       </c>
-      <c r="Z54" s="3">
-        <v>0</v>
-      </c>
       <c r="AA54" s="3">
         <v>0</v>
       </c>
@@ -4766,11 +4891,14 @@
       <c r="AF54" s="3">
         <v>0</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,50 +4968,51 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G57" s="3">
         <v>0</v>
       </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
       </c>
       <c r="K57" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L57" s="3">
         <v>600</v>
       </c>
       <c r="M57" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
       <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
@@ -4901,8 +5031,8 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
+      <c r="W57" s="3">
+        <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
@@ -4910,11 +5040,11 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>0</v>
       </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
@@ -4922,8 +5052,8 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD57" s="3">
-        <v>0</v>
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE57" s="3">
         <v>0</v>
@@ -4934,37 +5064,40 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4975,15 +5108,15 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
@@ -4996,8 +5129,8 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
@@ -5008,8 +5141,8 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5026,85 +5159,88 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G59" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I59" s="3">
-        <v>3900</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>2000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1900</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O59" s="3">
-        <v>600</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>500</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>600</v>
       </c>
       <c r="R59" s="3">
         <v>600</v>
       </c>
       <c r="S59" s="3">
+        <v>600</v>
+      </c>
+      <c r="T59" s="3">
         <v>300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1100</v>
-      </c>
-      <c r="U59" s="3">
-        <v>1000</v>
       </c>
       <c r="V59" s="3">
         <v>1000</v>
       </c>
       <c r="W59" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="X59" s="3">
         <v>300</v>
       </c>
       <c r="Y59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z59" s="3">
         <v>100</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
+      <c r="AA59" s="3">
+        <v>0</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
@@ -5115,89 +5251,92 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="3" t="s">
-        <v>3</v>
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF59" s="3">
+        <v>0</v>
       </c>
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2000</v>
       </c>
-      <c r="H60" s="3">
-        <v>2800</v>
-      </c>
       <c r="I60" s="3">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="J60" s="3">
+        <v>5100</v>
+      </c>
+      <c r="K60" s="3">
         <v>1000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1100</v>
-      </c>
-      <c r="U60" s="3">
-        <v>1000</v>
       </c>
       <c r="V60" s="3">
         <v>1000</v>
       </c>
       <c r="W60" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="X60" s="3">
         <v>300</v>
       </c>
       <c r="Y60" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z60" s="3">
         <v>100</v>
       </c>
-      <c r="Z60" s="3">
-        <v>0</v>
-      </c>
       <c r="AA60" s="3">
         <v>0</v>
       </c>
@@ -5216,16 +5355,19 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
         <v>600</v>
@@ -5240,10 +5382,10 @@
         <v>600</v>
       </c>
       <c r="I61" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J61" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="K61" s="3">
         <v>100</v>
@@ -5273,7 +5415,7 @@
         <v>100</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -5314,8 +5456,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5325,29 +5470,29 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>300</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>3400</v>
-      </c>
-      <c r="K62" s="3">
-        <v>300</v>
       </c>
       <c r="L62" s="3">
         <v>300</v>
       </c>
       <c r="M62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N62" s="3">
         <v>400</v>
@@ -5356,16 +5501,16 @@
         <v>400</v>
       </c>
       <c r="P62" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q62" s="3">
         <v>500</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -5409,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,80 +5848,83 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J66" s="3">
         <v>5700</v>
       </c>
-      <c r="I66" s="3">
-        <v>4600</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1500</v>
-      </c>
-      <c r="O66" s="3">
-        <v>1100</v>
       </c>
       <c r="P66" s="3">
         <v>1100</v>
       </c>
       <c r="Q66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R66" s="3">
         <v>1000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1200</v>
-      </c>
-      <c r="U66" s="3">
-        <v>1100</v>
       </c>
       <c r="V66" s="3">
         <v>1100</v>
       </c>
       <c r="W66" s="3">
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="X66" s="3">
         <v>300</v>
       </c>
       <c r="Y66" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z66" s="3">
         <v>100</v>
       </c>
-      <c r="Z66" s="3">
-        <v>0</v>
-      </c>
       <c r="AA66" s="3">
         <v>0</v>
       </c>
@@ -5786,11 +5943,14 @@
       <c r="AF66" s="3">
         <v>0</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,76 +6374,79 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2700</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-3300</v>
       </c>
       <c r="G72" s="3">
         <v>-3300</v>
       </c>
       <c r="H72" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="J72" s="3">
         <v>-5100</v>
       </c>
-      <c r="I72" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-4800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-300</v>
-      </c>
-      <c r="W72" s="3">
-        <v>200</v>
       </c>
       <c r="X72" s="3">
         <v>200</v>
       </c>
       <c r="Y72" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z72" s="3">
         <v>0</v>
@@ -6296,11 +6469,14 @@
       <c r="AF72" s="3">
         <v>0</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,80 +6766,83 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2200</v>
-      </c>
-      <c r="F76" s="3">
-        <v>1600</v>
       </c>
       <c r="G76" s="3">
         <v>1600</v>
       </c>
       <c r="H76" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I76" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J76" s="3">
         <v>-200</v>
       </c>
-      <c r="I76" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-100</v>
       </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
       <c r="O76" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P76" s="3">
         <v>400</v>
       </c>
       <c r="Q76" s="3">
+        <v>400</v>
+      </c>
+      <c r="R76" s="3">
         <v>300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>100</v>
       </c>
-      <c r="Z76" s="3">
-        <v>0</v>
-      </c>
       <c r="AA76" s="3">
         <v>0</v>
       </c>
@@ -6676,11 +6861,14 @@
       <c r="AF76" s="3">
         <v>0</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,180 +6962,186 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43677</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43585</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43496</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43404</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43312</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43220</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43131</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43039</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42947</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E81" s="3">
         <v>400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>600</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>1800</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-400</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-900</v>
       </c>
       <c r="Q81" s="3">
         <v>-900</v>
       </c>
       <c r="R81" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="S81" s="3">
         <v>-300</v>
       </c>
       <c r="T81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U81" s="3">
         <v>-400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-400</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
       <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>100</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
       <c r="AA81" s="3">
         <v>0</v>
       </c>
@@ -6966,11 +7160,14 @@
       <c r="AF81" s="3">
         <v>0</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7027,8 +7225,8 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7066,11 +7264,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -7090,8 +7288,8 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
+      <c r="AE83" s="3">
+        <v>0</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
@@ -7099,8 +7297,11 @@
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,77 +7787,80 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
         <v>300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>200</v>
       </c>
-      <c r="G89" s="3">
-        <v>-1500</v>
-      </c>
       <c r="H89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J89" s="3">
         <v>1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
+        <v>100</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M89" s="3">
+        <v>200</v>
+      </c>
+      <c r="N89" s="3">
+        <v>700</v>
+      </c>
+      <c r="O89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="T89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="U89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="V89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W89" s="3">
+        <v>300</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3">
         <v>100</v>
       </c>
-      <c r="K89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L89" s="3">
-        <v>200</v>
-      </c>
-      <c r="M89" s="3">
-        <v>700</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="O89" s="3">
-        <v>100</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-700</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V89" s="3">
-        <v>300</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X89" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
         <v>0</v>
       </c>
@@ -7666,11 +7882,14 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,31 +7923,32 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7743,11 +7963,11 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7763,11 +7983,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -7784,8 +8004,8 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -7796,11 +8016,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,19 +8215,22 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -8010,34 +8239,34 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M94" s="3">
         <v>100</v>
       </c>
       <c r="N94" s="3">
+        <v>100</v>
+      </c>
+      <c r="O94" s="3">
         <v>-400</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-200</v>
       </c>
       <c r="P94" s="3">
         <v>-200</v>
       </c>
       <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -8048,17 +8277,17 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -8081,11 +8310,14 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,31 +8351,32 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8214,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,8 +8741,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8508,70 +8753,70 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>700</v>
+      </c>
+      <c r="J100" s="3">
         <v>-600</v>
-      </c>
-      <c r="I100" s="3">
-        <v>300</v>
-      </c>
-      <c r="J100" s="3">
-        <v>200</v>
       </c>
       <c r="K100" s="3">
         <v>200</v>
       </c>
       <c r="L100" s="3">
+        <v>200</v>
+      </c>
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>900</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>300</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X100" s="3">
-        <v>100</v>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y100" s="3">
         <v>100</v>
       </c>
       <c r="Z100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -8591,11 +8836,14 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8617,8 +8865,8 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8656,8 +8904,8 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
@@ -8674,8 +8922,8 @@
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD101" s="3">
         <v>0</v>
@@ -8689,79 +8937,82 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>300</v>
+      </c>
+      <c r="I102" s="3">
+        <v>300</v>
+      </c>
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
+        <v>100</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>800</v>
+      </c>
+      <c r="O102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R102" s="3">
+        <v>100</v>
+      </c>
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="T102" s="3">
         <v>100</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>800</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-400</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P102" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>100</v>
-      </c>
-      <c r="R102" s="3">
-        <v>200</v>
-      </c>
-      <c r="S102" s="3">
-        <v>100</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>400</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X102" s="3">
-        <v>200</v>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y102" s="3">
         <v>200</v>
       </c>
       <c r="Z102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA102" s="3">
         <v>0</v>
@@ -8781,7 +9032,10 @@
       <c r="AF102" s="3">
         <v>0</v>
       </c>
-      <c r="AG102" s="3" t="s">
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
